--- a/tests/fixtures/test_cases/t101_fail_specific.xlsx
+++ b/tests/fixtures/test_cases/t101_fail_specific.xlsx
@@ -420,51 +420,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Region</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>B</t>
-        </is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C1">
+        <f>SUM(B2:B3)</f>
+        <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1">
-        <f>SUM(B3:B5)</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>100</v>
+          <t>Source: Statistics Canada.</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>x</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>suppressed</t>
         </is>
       </c>
     </row>
